--- a/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T01:04:27+00:00</t>
+    <t>2026-10-19T02:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/ValueSet-mii-vs-mikrobio-befundtyp-loinc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T02:33:36+00:00</t>
+    <t>2026-10-19T02:49:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
